--- a/Config/GameConfig/Datas/itemBase.xlsx
+++ b/Config/GameConfig/Datas/itemBase.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144F7BB8-6A79-4234-B2CA-D81274FC760A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,134 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>quality</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc</t>
+    </r>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>这是i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +159,57 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +217,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +527,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>